--- a/samples/номенклатура-пример.xlsx
+++ b/samples/номенклатура-пример.xlsx
@@ -413,24 +413,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,55 +457,60 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Вид изделия</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Цвет</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Размер</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Пол</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Состав</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Возрастная группа</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Бренд</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Страна</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Тип РД</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Номер РД</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Дата РД</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Срок действия</t>
         </is>
@@ -533,55 +539,60 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>футболка</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>чёрный</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>мужской</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>хлопок 100%</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>взрослая</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>DemoWear</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>декларация</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА01.В.10001/26</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2029-02-01</t>
         </is>
@@ -610,55 +621,60 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>футболка</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>чёрный</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>мужской</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>хлопок 100%</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>взрослая</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>DemoWear</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>декларация</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА01.В.10001/26</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2029-02-01</t>
         </is>
@@ -687,55 +703,60 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>футболка</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>чёрный</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>мужской</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>хлопок 100%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>взрослая</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>DemoWear</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>декларация</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА01.В.10001/26</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2029-02-01</t>
         </is>
@@ -764,55 +785,60 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>футболка</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>белый</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>мужской</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>хлопок 100%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>взрослая</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>DemoWear</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>декларация</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА01.В.10001/26</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2029-02-01</t>
         </is>
@@ -841,55 +867,60 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>футболка</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>белый</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>мужской</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>хлопок 100%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>взрослая</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>DemoWear</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>декларация</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА01.В.10001/26</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2029-02-01</t>
         </is>
@@ -918,55 +949,60 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>футболка</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>белый</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>мужской</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>хлопок 100%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>взрослая</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>DemoWear</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>декларация</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА01.В.10001/26</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2029-02-01</t>
         </is>
@@ -995,55 +1031,60 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>футболка</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>синий</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>мужской</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>хлопок 100%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>взрослая</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>DemoWear</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>декларация</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА01.В.10001/26</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2029-02-01</t>
         </is>
@@ -1072,55 +1113,60 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>футболка</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>синий</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>мужской</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>хлопок 100%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>взрослая</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>DemoWear</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>декларация</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА01.В.10001/26</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2029-02-01</t>
         </is>
@@ -1149,55 +1195,60 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>футболка</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>синий</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>мужской</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>хлопок 100%</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>взрослая</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>DemoWear</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>декларация</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА01.В.10001/26</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2029-02-01</t>
         </is>
@@ -1226,15 +1277,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>куртка</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>красный</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -1243,11 +1298,12 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Джемпер</t>
+          <t>Джемпер шерстяной</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1263,51 +1319,56 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
+          <t>джемпер</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>серый</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>женский</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>взрослая</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>DemoWear</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>декларация</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА01.В.10001/26</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2029-02-01</t>
         </is>
